--- a/mapping_D-07043.xlsx
+++ b/mapping_D-07043.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C9CAD6-355C-497F-B6BD-6F97E39B4212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43AD2E2-D42A-4023-825B-13058BA32E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
     <t>OP</t>
   </si>
   <si>
-    <t>API Utility Test V1</t>
+    <t>API OP Utility Test V1</t>
   </si>
 </sst>
 </file>
